--- a/output/full_scan/batch_seq2_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq2_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.69697854741072</v>
+        <v>70.6969785277908</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.79684231257076</v>
+        <v>21.79684230133299</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.050156976625568</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>70.85513923604471</v>
+        <v>70.85513918526703</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13.52742555964426</v>
+        <v>13.52742550952654</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>9.757713344797068</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.163444585889315</v>
+        <v>0.1634445860094874</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.80892736136661</v>
+        <v>65.80892716339439</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.65705714771831</v>
+        <v>27.65705713185908</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.742288973452979</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8334924201675884</v>
+        <v>0.8334924206482821</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>60.17011765547809</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.60279113214475</v>
+        <v>29.60279136527141</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.729802600786214</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3326972033769538</v>
+        <v>0.3326972034971396</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.29467301285925</v>
+        <v>73.29467301021711</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.92929537372731</v>
+        <v>22.92929530239626</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.38056560564696</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.465914428632123</v>
+        <v>0.4659144286513501</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77.9503658241799</v>
+        <v>77.9503657337314</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.83624249696273</v>
+        <v>33.83624243973894</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.429168811626341</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.0758785714156773</v>
+        <v>0.0758785714757607</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.38458207474285</v>
+        <v>69.38458204179767</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.99630021204972</v>
+        <v>37.99630028726808</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.83571993393895</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1093938018359589</v>
+        <v>0.1093938018720099</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.97078132319587</v>
+        <v>64.97078097781714</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.33744075584951</v>
+        <v>22.33744127644231</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.653405183233082</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.351973992481844</v>
+        <v>0.3519739930346414</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.19769330961114</v>
+        <v>67.19769327405224</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.86699674512041</v>
+        <v>29.86699677453029</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.9900706927793096</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>22.42074567018276</v>
+        <v>22.42074567330726</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.89384239001351</v>
+        <v>57.89384226845981</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13.51260972298406</v>
+        <v>13.51260976673128</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>2.927771851015974</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0210685476368157</v>
+        <v>0.0210685477321651</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.26911323171678</v>
+        <v>61.26911320533208</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32.0924772398178</v>
+        <v>32.09247727187469</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.696376105105591</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.113835739765285</v>
+        <v>0.1138357398013388</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.76487762587419</v>
+        <v>70.76487757175592</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.34536643656106</v>
+        <v>31.34536652212149</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>5.469847179428196</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1447751916314974</v>
+        <v>0.1447751917420565</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.7862255190241</v>
+        <v>66.78622548400679</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>26.04169747474713</v>
+        <v>26.0416975121821</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.621360999886836</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.0049358598893634</v>
+        <v>-0.0049358599374381</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>75.64973485750943</v>
+        <v>75.64973483848814</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>55.8472292699412</v>
+        <v>55.84722927488647</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.5555876306440686</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07008915275846871</v>
+        <v>0.07008915280654</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>78.06543857705439</v>
+        <v>78.06543866146744</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.11047766227894</v>
+        <v>20.11047766373548</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>6.537332830060383</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1472900160058168</v>
+        <v>0.1472900159577448</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.40651726834367</v>
+        <v>58.40651718272325</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.769258559192</v>
+        <v>30.76925853854352</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.8766075667246659</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>80.5120860333456</v>
+        <v>80.51208602079939</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>38.5194634120212</v>
+        <v>38.51946343015077</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>3.728189983305968</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.700468179661648</v>
+        <v>1.70046817973375</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>75.40066069681978</v>
+        <v>75.40066066194382</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>41.42495302764531</v>
+        <v>41.42495297315796</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5.800896158283987</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.131299001100288</v>
+        <v>1.131299001352654</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.62356709321925</v>
+        <v>61.62356706072766</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.56529693444012</v>
+        <v>13.56529684168765</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>5.260502587276197</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1395883822077337</v>
+        <v>0.1395883821716807</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>973.6513957416138</v>
+        <v>973.6513957416132</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>30.2</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.85775317528334</v>
+        <v>60.8577531127334</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.45413307845547</v>
+        <v>17.4541330292278</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>3.344961835751864</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1641025817222132</v>
+        <v>0.1641025818423828</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.07622565281752</v>
+        <v>60.0762257301446</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.55741114744697</v>
+        <v>14.55741132647476</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>2.404892254375318</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4152313796460827</v>
+        <v>0.4152313795499467</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>66.84500154961199</v>
+        <v>66.84500150091876</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.06895165741626</v>
+        <v>20.06895167896093</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.8042412362517974</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>131.8616783395892</v>
+        <v>131.8616783455981</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>951.3965672697904</v>
+        <v>951.3965672697898</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>9.789999999999999</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>72.3958748042737</v>
+        <v>72.39587427739552</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>35.04607702830466</v>
+        <v>35.04607801182163</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>2.032785633433351</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1626800095835978</v>
+        <v>0.1626800104007743</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>64.11115356424648</v>
+        <v>64.11115353169598</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.08489229647993</v>
+        <v>21.08489227540549</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.471831358967866</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5043709250941073</v>
+        <v>0.5043709251181459</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>925.3641971591162</v>
+        <v>925.3641971591156</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>130.5</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.9903567243828</v>
+        <v>60.9903566938087</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.0273066762376</v>
+        <v>18.02730665909836</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.794526844836611</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.771090067762998</v>
+        <v>1.771090067811074</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.10510511045533</v>
+        <v>56.10510509073833</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.28794151450424</v>
+        <v>20.28794148257948</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6855393377297392</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>9.927824668804275</v>
+        <v>9.927824670486755</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>902.7805051352684</v>
+        <v>902.7805051352696</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>96.40000000000001</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.72136707695915</v>
+        <v>66.72136713171847</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.4018071898946</v>
+        <v>38.4018073437171</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.6050049021493942</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4356678442179644</v>
+        <v>0.4356678440256876</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>70.68806646794081</v>
+        <v>70.68806642606705</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.06229071423819</v>
+        <v>16.06229073239338</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>3.992830451904892</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>76.85470301633768</v>
+        <v>76.85470307965693</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.39262119264959</v>
+        <v>23.39262117184775</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>12.66770963283941</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1680771318847</v>
+        <v>0.168077131848649</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>897.0282112996445</v>
+        <v>897.0282112996446</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>127</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.65492648995042</v>
+        <v>58.65492645388071</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.00692459938032</v>
+        <v>21.00692460893837</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.016053128320619</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4668886910416345</v>
+        <v>0.4668886909935641</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>887.5108733252731</v>
+        <v>887.5108733252729</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>57</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>72.15681535630839</v>
+        <v>72.15681538583432</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.20478004790316</v>
+        <v>31.20478002071297</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.276712455680139</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.7080423621675369</v>
+        <v>0.7080423622636767</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>876.1929479604452</v>
+        <v>876.1929479604451</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>2550</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>61.51112047504149</v>
+        <v>61.51112048464972</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>28.25042998457734</v>
+        <v>28.25042992547441</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.061155738334968</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>72.35124283683102</v>
+        <v>72.35124286440808</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>55.25464461673244</v>
+        <v>55.25464457620269</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.9391919258737972</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7590839833141509</v>
+        <v>0.7590839833021388</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>70.2533670287394</v>
+        <v>70.25336697441413</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37.16639796701927</v>
+        <v>37.16639806367694</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.8061136203541167</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.011844057043596</v>
+        <v>-0.0118440565629041</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>76.90165413103415</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.73289267619676</v>
+        <v>27.73289264885621</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.448299181756732</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1270750890191936</v>
+        <v>0.1270750889951586</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>844.58808559478</v>
+        <v>844.5880855947808</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>45.2</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.86374034884554</v>
+        <v>64.86374024752078</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.54178579768772</v>
+        <v>18.54178581969857</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.90721936349136</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4673649948038064</v>
+        <v>0.4673649949119702</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>840.6934482602112</v>
+        <v>840.6934482602071</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>33.35</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.63017265650421</v>
+        <v>58.6301728133085</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.54571154632662</v>
+        <v>22.54571150124332</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>2.090840240916856</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0194460560977906</v>
+        <v>0.0194460559655973</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>840.3435102363843</v>
+        <v>840.3435102363846</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>168</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.68509733093016</v>
+        <v>54.68509725700382</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.20523819507975</v>
+        <v>16.20523823321872</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.7680883550901754</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0329223346250522</v>
+        <v>-0.03292233414437</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>835.433782075717</v>
+        <v>835.4337820757169</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>11.6</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>63.29189243657944</v>
+        <v>63.2918923329668</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.28547497253741</v>
+        <v>35.28547516058155</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.229323294805348</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.058851253848043</v>
+        <v>0.0588512539081305</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>68.73701976753676</v>
+        <v>68.73701973819344</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>43.05667174610002</v>
+        <v>43.05667187210293</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.404300607088356</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3370733298657484</v>
+        <v>0.337073329961886</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>64.30021896581808</v>
+        <v>64.30021884187521</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.76140547705675</v>
+        <v>22.76140520313474</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>3.60781576547095</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.8074111339182779</v>
+        <v>0.8074111343388819</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>62.00031246637297</v>
+        <v>62.00031228934998</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.12610095198034</v>
+        <v>33.12610093471487</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.06742840992178</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.534767668814167</v>
+        <v>1.534767670256247</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>72.83038809015456</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>52.97022619897933</v>
+        <v>52.97022635976182</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.4538694229049278</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.6388727494979429</v>
+        <v>0.6388727495099595</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>70.31971846243876</v>
+        <v>70.31971846645672</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>55.16282366740788</v>
+        <v>55.16282367062867</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.5347246496116023</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.5278657846026267</v>
+        <v>-0.5278657846146508</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.73661600337777</v>
+        <v>58.73661596001596</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.53991762388037</v>
+        <v>16.53991763732756</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4503758500879788</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>19.25405812875562</v>
+        <v>19.25405812923653</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.57237241740625</v>
+        <v>54.57237240296578</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.19736142474463</v>
+        <v>22.19736148029027</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>3.697312604973099</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.29019406722384</v>
+        <v>0.2901940670796348</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>794.0843697197549</v>
+        <v>794.0843697197553</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1305</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>64.72094977167748</v>
+        <v>64.72094966808447</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>34.60539862578553</v>
+        <v>34.6053986408518</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5812027673440475</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>16.71029754096742</v>
+        <v>16.71029754457264</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>793.9464011455752</v>
+        <v>793.9464011455755</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>248</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.98463159012458</v>
+        <v>61.98463158043403</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.18105095732694</v>
+        <v>17.18105095732693</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.995779094897068</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.575041644509958</v>
+        <v>2.575041644461859</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.75111934921522</v>
+        <v>53.75111929580827</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.10425066591252</v>
+        <v>23.10425070435561</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.4594253552742053</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.96264440112976</v>
+        <v>54.96264425429217</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.21860701966754</v>
+        <v>20.21860684392485</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.040101593052447</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0882207954921938</v>
+        <v>0.08822079573253649</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.74555091103088</v>
+        <v>57.74555078334708</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.69429903817878</v>
+        <v>24.69429892457171</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.52499085448573</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.786703175629713</v>
+        <v>1.786703177840917</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>69.07353921123237</v>
+        <v>69.07353917494305</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>37.8731116856922</v>
+        <v>37.8731116760931</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.4201468887200273</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3633982793801382</v>
+        <v>0.3633982794161925</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>60.64682276927079</v>
+        <v>60.6468227657671</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.16468075843608</v>
+        <v>23.16468075129988</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.7649147407581803</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.07945350044784</v>
+        <v>1.079453500688025</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>764.3809673860998</v>
+        <v>764.3809673861</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>63.9</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>61.845342086758</v>
+        <v>61.84534189692637</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.52040118694451</v>
+        <v>16.52040108601704</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>5.639649615856536</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5617341387094392</v>
+        <v>0.5617341395266142</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>749.0879903528852</v>
+        <v>749.0879903528864</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>532</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>56.66330149641151</v>
+        <v>56.66330149145651</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8.868007195491016</v>
+        <v>8.868007246211349</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.49330013179631</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.9622057140829644</v>
+        <v>0.9622057139266992</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>59.52980402477831</v>
+        <v>59.52980415010035</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.88524909308522</v>
+        <v>15.88524912026582</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>4.055689306449837</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.116608166661765</v>
+        <v>0.1166081665416007</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.73892302247501</v>
+        <v>54.73892304925201</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21.38907863274756</v>
+        <v>21.38907856726555</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6903307218807591</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0020681838074619</v>
+        <v>-0.0020681838314967</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>731.0439112241195</v>
+        <v>731.0439112241196</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>13.6</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.68148947043272</v>
+        <v>56.68148937168154</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.86454320927947</v>
+        <v>28.86454326087902</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.8945635880592142</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.07346273234408079</v>
+        <v>0.0734627324642535</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.83202897054743</v>
+        <v>55.83202898440648</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.42316871127201</v>
+        <v>24.42316873085189</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.746483292741697</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1667255896503248</v>
+        <v>0.1667255896743606</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>724.6206536917366</v>
+        <v>724.6206536917457</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>48.05</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>59.32426704170534</v>
+        <v>59.32426707096149</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.89138985084521</v>
+        <v>22.89138982618795</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.6008269293035824</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1241607702664761</v>
+        <v>0.1241607704106865</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>56.45102925616469</v>
+        <v>56.45102914593841</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>29.34443207839126</v>
+        <v>29.34443216193447</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.3383305593505533</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0059085840391988</v>
+        <v>0.005908584171385</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>65.34878572847886</v>
+        <v>65.34878577430035</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.95907328364075</v>
+        <v>14.95907328156988</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1.146803380232041</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>68.04799329266442</v>
+        <v>68.0479934342067</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>43.51684716883082</v>
+        <v>43.51684717252802</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4913067528545715</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1523803766642293</v>
+        <v>0.1523803765921233</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.68936764771476</v>
+        <v>63.68936763039161</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>39.586281362663</v>
+        <v>39.58628136155515</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.3606996580771582</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.474923309585427</v>
+        <v>0.4749233096334979</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>683.2187030750258</v>
+        <v>683.2187030750296</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>61</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>64.47412833324449</v>
+        <v>64.47412841156367</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.45805471237915</v>
+        <v>21.45805472138431</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.493132248375586</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.7523088049909792</v>
+        <v>0.7523088050630815</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.73681416326853</v>
+        <v>53.73681414925158</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.40328664526562</v>
+        <v>21.40328668932014</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5619655490152515</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1843459166203601</v>
+        <v>0.1843459167405129</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>662.1250001220924</v>
+        <v>662.1250001220927</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>39.1</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>59.09106118781794</v>
+        <v>59.09106107576131</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.85982589892376</v>
+        <v>22.85982585097885</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1.218070463086605</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2147097446405061</v>
+        <v>0.2147097448087442</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>61.73906997580899</v>
+        <v>61.73906996871282</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.67873954900934</v>
+        <v>28.67873983777387</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.765013461724687</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.331622813702209</v>
+        <v>0.3316228138704531</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58.42864003574621</v>
+        <v>58.42863993264352</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.1495574637109</v>
+        <v>12.1495575220202</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1.839079924947858</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>64.11326900549405</v>
+        <v>64.11326905000564</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>36.62824673255307</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.9597572365804</v>
+        <v>54.95975703398481</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.8253962770133</v>
+        <v>11.8253960377289</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.8723729535688053</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3193520485612935</v>
+        <v>0.319352049486635</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.07155213009751</v>
+        <v>55.07155213327184</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.81873654884172</v>
+        <v>23.8187366135787</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.3759796481843491</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0011456611559688</v>
+        <v>-0.0011456612280724</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>623.1903244695574</v>
+        <v>623.1903244695524</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>45.45</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>59.18677883455089</v>
+        <v>59.18677872267093</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.51370927984534</v>
+        <v>30.51370926361729</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.374370278912721</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.4529784706741311</v>
+        <v>0.4529784708664128</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>52.05528733464764</v>
+        <v>52.05528726165667</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>30.42588253451991</v>
+        <v>30.4258825289002</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.4113142352193555</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0977879182790297</v>
+        <v>-0.09778791799060529</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>54.22728593645652</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.65847819471126</v>
+        <v>32.65847817504179</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.4449161402678344</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1126876389078836</v>
+        <v>-0.112687639028064</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>607.8807573410375</v>
+        <v>607.8807573410363</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>13.95</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>57.54458890446251</v>
+        <v>57.54458898141232</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>30.84094828212283</v>
+        <v>30.8409482645148</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.9465482074209832</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0307031357674805</v>
+        <v>0.0307031357554625</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.49019287715407</v>
+        <v>53.49019281654184</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>30.73126404361513</v>
+        <v>30.73126401593165</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.7880032068577045</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.3428020073330802</v>
+        <v>-0.3428020070927258</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>69.87963041086297</v>
+        <v>69.87963036469809</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>33.86784210647347</v>
+        <v>33.86784211853557</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.7903549793550418</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.390662546537154</v>
+        <v>0.3906625465852258</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>599.3890108156893</v>
+        <v>599.3890108156889</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>103.5</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.30527687565885</v>
+        <v>53.3052768786897</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25.96580234307005</v>
+        <v>25.96580234822581</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1.140821155582824</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.446733574753966</v>
+        <v>1.446733574705897</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>59.6427258846136</v>
+        <v>59.6427259074789</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>33.15692337593631</v>
+        <v>33.15692335159258</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.7352901866805018</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4283782949898445</v>
+        <v>0.4283782942688816</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>591.081360295994</v>
+        <v>591.0813602959939</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>103</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>55.17033215513696</v>
+        <v>55.17033214299956</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>34.9905736670969</v>
+        <v>34.99057360163101</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.3745224919001232</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3859021425132631</v>
+        <v>-0.3859021424051088</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.322041569808</v>
+        <v>53.32204159348924</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>33.97158195627472</v>
+        <v>33.97158186658871</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.7119144467689686</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.7875925174000686</v>
+        <v>-0.7875925169554181</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>577.4582113845047</v>
+        <v>577.4582113845046</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>63.6</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>55.07085762238452</v>
+        <v>55.0708576417057</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.101201826703855</v>
+        <v>9.101201882539851</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.7954403260761205</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0177009148043621</v>
+        <v>-0.0177009149005076</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.7665830458464</v>
+        <v>54.76658303426942</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>47.09762468231531</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>59.86307465917677</v>
+        <v>59.8630746907764</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>36.25298770149131</v>
+        <v>36.25298770293043</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.4416549825938335</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.44989526588822</v>
+        <v>39.44989509012801</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29.72435377963868</v>
+        <v>29.72435365819903</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.5288837128112573</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.6175189635225111</v>
+        <v>-0.6175189632821623</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>558.0504546448346</v>
+        <v>558.0504546448349</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>16.75</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>61.08658499885862</v>
+        <v>61.0865849305733</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>30.94795783496576</v>
+        <v>30.94795787476396</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.3759992456546565</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0719092793102927</v>
+        <v>0.0719092793944125</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>60.07408908166051</v>
+        <v>60.07408907969806</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45.05485900769776</v>
+        <v>45.05485900086798</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.487137903322783</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1533309665565063</v>
+        <v>0.153330966592561</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>61.97983735955878</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.54344015707824</v>
+        <v>12.54344012496418</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>2.894345787544123</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0049325055482594</v>
+        <v>-0.0049325055242297</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>539.3594100469443</v>
+        <v>539.3594100469446</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>90.09999999999999</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>60.61936156385192</v>
+        <v>60.61936135824927</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.02484357144404</v>
+        <v>14.02484351295958</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.9895133602030154</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0168962633396225</v>
+        <v>0.0168962633636697</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>533.7143205346744</v>
+        <v>533.7143205346745</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>25.6</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.09879441845206</v>
+        <v>54.09879442131338</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.6747512311098</v>
+        <v>11.67475134884709</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.2414347354249721</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.3344184503785072</v>
+        <v>-0.3344184504608876</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.93904892268159</v>
+        <v>52.93904860229304</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.41565067829892</v>
+        <v>19.41565068791679</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.920881832319831</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0230672517494697</v>
+        <v>0.0230672521340192</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>54.41666463812797</v>
+        <v>54.41666440508843</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.62872337238622</v>
+        <v>14.62872345796</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.9323832194344922</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0507502558922213</v>
+        <v>0.0507502561926557</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.51767289209747</v>
+        <v>43.51767297431249</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.2839410650463</v>
+        <v>12.28394113994499</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.8034750937866295</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.75272341765245</v>
+        <v>50.75272340832759</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>21.15888517832684</v>
+        <v>21.15888513820208</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.6294867027924709</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.4495184930061402</v>
+        <v>0.4495184937271652</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.29350831991901</v>
+        <v>51.29350834448461</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>25.02132502203893</v>
+        <v>25.02132532167022</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.4695278885699097</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.525334610903707</v>
+        <v>-1.525334611095989</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>523.066201646119</v>
+        <v>523.0662016461188</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>32</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>53.1014594900262</v>
+        <v>53.10145945540598</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.59058689164702</v>
+        <v>20.59058681424054</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.784158579155516</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1999173377424782</v>
+        <v>0.1999173377905478</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>522.6440589510826</v>
+        <v>522.6440589510792</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>26</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.97272904913412</v>
+        <v>49.97272911192626</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.6306691199204</v>
+        <v>22.63066916141491</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.6750270240994036</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.131862190531547</v>
+        <v>0.1318621905676002</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.84528040263005</v>
+        <v>42.84528051556474</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28.02073135537066</v>
+        <v>28.02073139572019</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>1.789293360985839</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0019982965959939</v>
+        <v>0.0019982965719587</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>512.1227088951669</v>
+        <v>512.1227088951664</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>177</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.4287864073871</v>
+        <v>51.42878638899688</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.899386158406406</v>
+        <v>9.899386139608094</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.8427926590377181</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.4323904006512542</v>
+        <v>0.4323904008194976</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>508.4827004317915</v>
+        <v>508.4827004317916</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>53.9</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>56.6589851917044</v>
+        <v>56.65898512902289</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.61899022131295</v>
+        <v>15.61899029812576</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.6396001350760796</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1956000398282866</v>
+        <v>0.1956000400686412</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.32378688520615</v>
+        <v>53.32378706122299</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.94132742251655</v>
+        <v>24.94132730484269</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.7075591169154314</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0017741987243028</v>
+        <v>0.0017741986281654</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>503.4572462264183</v>
+        <v>503.4572462264177</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>1205</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.89936301539124</v>
+        <v>37.89936297793829</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>35.03234480955805</v>
+        <v>35.03234479572543</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>2.133756862167808</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>4.287157838332355</v>
+        <v>4.287157838091915</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>56.15599035439581</v>
+        <v>56.1559902309948</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.33756475655024</v>
+        <v>18.33756472154077</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.027090575173112</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>34.54163006158142</v>
+        <v>34.54163007239682</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>502.1353025501829</v>
+        <v>502.1353025501809</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>23.2</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>66.15112158256821</v>
+        <v>66.15112156969101</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.33756110722239</v>
+        <v>24.33756109271896</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>2.120333525939616</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.3825845526795515</v>
+        <v>0.3825845527156034</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>54.57357650308493</v>
+        <v>54.57357646895836</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>42.95077036989759</v>
+        <v>42.95077045105329</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.189222188404608</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2479103409067256</v>
+        <v>-0.2479103411350538</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>55.58901387606442</v>
+        <v>55.58901386147213</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.26699067788929</v>
+        <v>10.26699067233446</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.3999031970024451</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0556899551156766</v>
+        <v>0.0556899550916394</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>56.92102377677658</v>
+        <v>56.92102386158015</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>38.67547833493807</v>
+        <v>38.67547816976395</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.4341555846144904</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1463785517476543</v>
+        <v>0.1463785516515181</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>52.3521979364142</v>
+        <v>52.35219777113987</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>27.22347394989353</v>
+        <v>27.22347390561015</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.4255534380387534</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.239982902883899</v>
+        <v>0.239982903436695</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>54.43426340522662</v>
+        <v>54.43426335293896</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>26.86928409963727</v>
+        <v>26.86928408995564</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.2166574056877103</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0354950146662439</v>
+        <v>0.0354950147263335</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>53.20036304751547</v>
+        <v>53.20036301494498</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>34.6435069524039</v>
+        <v>34.64350692434454</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.121689066537526</v>
@@ -6491,7 +6491,7 @@
         <v>48.21987768428736</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.97106825154627</v>
+        <v>24.97106817672388</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.2044100277812277</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.08442954979641761</v>
+        <v>-0.0844295498204525</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>481.9254084109454</v>
+        <v>481.9254084109452</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>71.3</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.81944524090136</v>
+        <v>49.81944532945575</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>22.06292234174703</v>
+        <v>22.06292246524904</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.5257442256980962</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0763880661483787</v>
+        <v>-0.07638806612433929</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>63.92785227943313</v>
+        <v>63.92785233660975</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>30.43123034272396</v>
+        <v>30.43123042153304</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.2612164520970935</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.4996627445651108</v>
+        <v>0.4996627447453708</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>471.2189090723916</v>
+        <v>471.2189090723925</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>57.5</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>31.35555618785297</v>
+        <v>31.35555608549262</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>29.03175279045281</v>
+        <v>29.03175285391853</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.955630800823152</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2201083778943906</v>
+        <v>-0.2201083777622046</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.02408291019178</v>
+        <v>43.02408279066452</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.2896294698051</v>
+        <v>15.28962937917419</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.963220081730622</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.1062538632018979</v>
+        <v>-0.106253863141813</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>47.02044856659924</v>
+        <v>47.0204485883163</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.87573374635591</v>
+        <v>20.87573376196846</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.4257855309346145</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1118936119107664</v>
+        <v>-0.1118936120309413</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.8590543275952</v>
+        <v>44.85905433328332</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>22.49227171973693</v>
+        <v>22.49227166398949</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.2646611503286855</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.58038839729632</v>
+        <v>46.580388149901</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.90484816212675</v>
+        <v>15.90484845318999</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.3374989040236856</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1304706524176538</v>
+        <v>-0.1304706520675303</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>459.7621487109981</v>
+        <v>459.7621487109975</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>10615</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>35.98027364014499</v>
+        <v>35.98027362269187</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.32273332199614</v>
+        <v>17.32273332104624</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>3.95654411466248</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-150.5332389744722</v>
+        <v>-150.533238962454</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>458.1555234526627</v>
+        <v>458.1555234526629</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>56.6</v>
@@ -6968,7 +6968,7 @@
         <v>57.69469752470714</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>23.49022439048097</v>
+        <v>23.49022433350489</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5634151054689247</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.3916712065936459</v>
+        <v>0.3916712066657538</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>457.8447461052697</v>
+        <v>457.84474610527</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>22.7</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>56.31658857032548</v>
+        <v>56.31658827568925</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.8654480642761</v>
+        <v>17.86544832121773</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6511572474986064</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0636519832948448</v>
+        <v>0.0636519834751031</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>49.36877392634661</v>
+        <v>49.36877389589018</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.27923845948078</v>
+        <v>13.27923841306681</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.8725777182545483</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.5391092210027485</v>
+        <v>-0.5391092202817708</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>53.60686987231132</v>
+        <v>53.60686981793</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>26.09106096324994</v>
+        <v>26.09106099206993</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.695826746490306</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.3172446624886265</v>
+        <v>0.3172446625006517</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>49.81817827245396</v>
+        <v>49.81817818112616</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>22.92803991037693</v>
+        <v>22.92803995358335</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.551481505349897</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0550143666217233</v>
+        <v>0.0550143666457602</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>48.8971460072347</v>
+        <v>48.8971462499167</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>20.14488706326325</v>
+        <v>20.14488707103511</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.5340678540194213</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0739413995018277</v>
+        <v>0.07394139944173971</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>52.97728261144287</v>
+        <v>52.97728258546022</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>20.63517021688335</v>
+        <v>20.63517014800916</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.2703088683763771</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0430559119299614</v>
+        <v>0.0430559119179431</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>51.7588398665382</v>
+        <v>51.7588397943102</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>11.75911359265421</v>
+        <v>11.75911353642575</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.9792368831292652</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0206421351158647</v>
+        <v>-0.0206421351399003</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>447.1988060909582</v>
+        <v>447.1988060909583</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>249</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.40049469938324</v>
+        <v>46.40049458720836</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>9.532539524677381</v>
+        <v>9.532539463122466</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.168195982228217</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0138060043712971</v>
+        <v>-0.0138060036502682</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>44.7765239434025</v>
+        <v>44.77652411683721</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>20.54283974109728</v>
+        <v>20.5428397734313</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.9616482745057509</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0518046052911883</v>
+        <v>-0.0518046052721198</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>24.03605119834349</v>
+        <v>24.03432119901529</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>38.87085434909748</v>
+        <v>38.87294737298616</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>4.024376545896833</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0987303952946339</v>
+        <v>0.09873290392748731</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>55.72557367377543</v>
+        <v>55.72557355253581</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15.41112073632401</v>
+        <v>15.41112071007164</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.7300410989935601</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0386622563055823</v>
+        <v>0.0386622562935657</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>46.69715829614802</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>17.93840969004774</v>
+        <v>17.93840964840968</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.3760184476049382</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0203460707586199</v>
+        <v>-0.0203460708066868</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>48.28803745457112</v>
+        <v>48.28803748702644</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>6.892481988026151</v>
+        <v>6.892482137008077</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.6391031392830127</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.0774117790174943</v>
+        <v>-0.07741177904153081</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>428.9245117543473</v>
+        <v>428.9245117543489</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>44.5</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>52.74450192617943</v>
+        <v>52.74450180856078</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>14.5142073315936</v>
+        <v>14.5142072986972</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>1.754963877777169</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.204555589278088</v>
+        <v>0.2045555894222898</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>426.6850424904872</v>
+        <v>426.6850424905011</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>45.9</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>57.5160882164552</v>
+        <v>57.51608812224055</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>24.41284942971411</v>
+        <v>24.41284946376768</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.9750554966095516</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.6967932138033582</v>
+        <v>0.6967932138153766</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.0985515180143</v>
+        <v>45.09855125828554</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>22.82242896477932</v>
+        <v>22.82242907798657</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.5308092195120614</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.9028308647555868</v>
+        <v>0.902830866077454</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>52.3578468517879</v>
+        <v>52.35784695348343</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>24.81028953878271</v>
+        <v>24.8102899166109</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.7161645127597153</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.0055533319221961</v>
+        <v>0.0055533319582471</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>413.0707072688672</v>
+        <v>413.0707072688671</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>216</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>47.24263650124128</v>
+        <v>47.24263648218859</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>18.88833222413841</v>
+        <v>18.88833208505632</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.3970954505855907</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-3.122973029711116</v>
+        <v>-3.122973029518844</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>49.86502273905976</v>
+        <v>49.86502285719195</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>10.22648367273964</v>
+        <v>10.22648372452912</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>1.512229692359781</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.004408596923186</v>
+        <v>0.0044085968751145</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>405.0154942007145</v>
+        <v>405.0154942007146</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>28.6</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>52.2084744528261</v>
+        <v>52.20847441699673</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>24.4181020190031</v>
+        <v>24.41810212744729</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>1.822217992407391</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.3710705492414406</v>
+        <v>0.3710705494457347</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>396.5327839313492</v>
+        <v>396.5327839313497</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>30.55</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>47.66569925162564</v>
+        <v>47.6656992197427</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>53.65182141879215</v>
+        <v>53.65182138998009</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.6674085954633237</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.0174599910730122</v>
+        <v>0.017459991145116</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>395.4419187087176</v>
+        <v>395.4419187087179</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>142.5</v>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>49.8034765559716</v>
+        <v>49.80347649992623</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>9.401697952771574</v>
+        <v>9.401697966651597</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.3740055333566994</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.2619549204689316</v>
+        <v>0.2619549207333104</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>45.81176852255614</v>
+        <v>45.8117685850546</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>13.38389332830762</v>
+        <v>13.38389328849788</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.4116218253576071</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.1356766613522408</v>
+        <v>-0.1356766614603987</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>387.9923413076359</v>
+        <v>387.9923413080167</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>12.85</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>50.21857113120752</v>
+        <v>50.21857112671673</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>7.386552518356844</v>
+        <v>7.386552472275087</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>5.029144803835003</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.07036566903284019</v>
+        <v>0.0703656689847732</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>387.4116007865583</v>
+        <v>387.4116007865584</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>27</v>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45.83626463081643</v>
+        <v>45.83626454453066</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>33.01455020553193</v>
+        <v>33.01455024604141</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.31431438537231</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.2917877248629157</v>
+        <v>-0.2917877247787954</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>385.4901328411356</v>
+        <v>385.4901328411357</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>39.6</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>50.7138795032587</v>
+        <v>50.71387938571397</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>25.25916577913516</v>
+        <v>25.25916585239307</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.3753885481653372</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.0268826257167298</v>
+        <v>0.0268826256806796</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>384.7148651181372</v>
+        <v>384.7148651181376</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>226</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>43.9866327989569</v>
+        <v>43.98663269257965</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>13.79925077968596</v>
+        <v>13.79925085256409</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>2.560896459869394</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.4124653412321353</v>
+        <v>-0.4124653415926502</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>380.6785501840869</v>
+        <v>380.6785501840868</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>30.65</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>44.20441673672275</v>
+        <v>44.20441648957512</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5.974732201085905</v>
+        <v>5.974732110350656</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.7409489433726762</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.0247217902136896</v>
+        <v>0.0247217903218471</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>378.6103940003461</v>
+        <v>378.6103940003466</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>18</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>40.0721794435143</v>
+        <v>40.07217960687476</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>29.82087498218322</v>
+        <v>29.82087509186867</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.081252808683655</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.0050638535572625</v>
+        <v>0.0050638535212127</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46.22666659686201</v>
+        <v>46.22666660157714</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>11.90831543736023</v>
+        <v>11.90831538480804</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.0453972404795961</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.0634752746624741</v>
+        <v>-0.06347527478265171</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>18.73931191796406</v>
+        <v>18.73931195684786</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>37.96482366367272</v>
+        <v>37.96482373289084</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>1.2864006971189</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-2.715888166142959</v>
+        <v>-2.715888166503469</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>357.2770772005701</v>
+        <v>357.27707720057</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>30</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45.56508963493093</v>
+        <v>45.56508946598233</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>27.90997967576447</v>
+        <v>27.90998003414292</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>1.712822402224763</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.07203553261365191</v>
+        <v>0.0720355330461586</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>356.5639832672877</v>
+        <v>356.563983267284</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>116</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>42.61026129201282</v>
+        <v>42.61026128483373</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>7.500204700690421</v>
+        <v>7.500204686433761</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>1.41300129487868</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.0458956770998346</v>
+        <v>0.045895677123847</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>38.16553543480347</v>
+        <v>38.16553539570138</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>19.66644081413513</v>
+        <v>19.66644089657781</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>1.155266181881659</v>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>48.18298468700461</v>
+        <v>48.18298465196415</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>9.697828735808608</v>
+        <v>9.697828723487657</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.781419997609018</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0509544479115397</v>
+        <v>0.0509544480076787</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>36.88367245674343</v>
+        <v>36.88367248701125</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>34.96626812816813</v>
+        <v>34.96626820731215</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.8988934262792878</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>50.73577579965161</v>
+        <v>50.73577598566269</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>17.40721646406193</v>
+        <v>17.40721637545301</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.8419443747967681</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.7780225953964446</v>
+        <v>0.7780225938341925</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>48.5783480456276</v>
+        <v>48.57834806140723</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>4.702270776746934</v>
+        <v>4.702270957129699</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.5237840809352778</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.0076996132077124</v>
+        <v>-0.0076996132557808</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>45.60491408188696</v>
+        <v>45.60491394297969</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12.61833641558077</v>
+        <v>12.61833636686403</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.7013078794206757</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.8406488772313461</v>
+        <v>0.8406488792742701</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>42.3241250260354</v>
+        <v>42.32412488741552</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>13.79635014217196</v>
+        <v>13.7963502049795</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.6237450916658008</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.0244402890182144</v>
+        <v>0.0244402890302314</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46.75776465459716</v>
+        <v>46.75776433005495</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>16.96744855455907</v>
+        <v>16.96744868014773</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.9573161503925974</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.0157307623753574</v>
+        <v>0.0157307624714952</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>35.22706966175546</v>
+        <v>35.22706951472695</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>36.39429354700759</v>
+        <v>36.39429372313865</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.5544411990217508</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.07076182538550339</v>
+        <v>0.0707618256018106</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>341.4399979409575</v>
+        <v>341.4399979409576</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>91.3</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>47.18746832414548</v>
+        <v>47.18746819733204</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>23.64901510265837</v>
+        <v>23.64901512353341</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.7409203380873602</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.1966934922761652</v>
+        <v>0.1966934938864855</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>339.9224912343536</v>
+        <v>339.9224912343544</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>15.85</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>32.8405498563495</v>
+        <v>32.84054988145313</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>12.54486277049481</v>
+        <v>12.54486301890202</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>1.531536728318991</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.0406289208010784</v>
+        <v>-0.0406289205951213</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>18.60120746917961</v>
+        <v>18.60120708347173</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>24.61350942753201</v>
+        <v>24.61350941098277</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>2.675647899702847</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.014805420806196</v>
+        <v>0.0148054210465402</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>45.40588640810953</v>
+        <v>45.40588620204734</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>14.2753725074748</v>
+        <v>14.27537248278229</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.4032159575690649</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.0367566937097854</v>
+        <v>0.0367566943346844</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>327.9752126474688</v>
+        <v>327.9752126474706</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>12.5</v>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>49.60471909672649</v>
+        <v>49.60471913129789</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>22.4654167640839</v>
+        <v>22.46541676962901</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.3322446377035078</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>0.0323941984007915</v>
+        <v>0.0323941984248243</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>41.78585657843308</v>
+        <v>41.78585651307277</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>26.8926568133752</v>
+        <v>26.89265702285704</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.8022888498000235</v>
@@ -9565,7 +9565,7 @@
         <v>37.71785933744851</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>15.77019382632766</v>
+        <v>15.77019391385217</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.5583916836275373</v>
@@ -9601,7 +9601,7 @@
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>316.1008183386726</v>
+        <v>316.1008183386728</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>52.4</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>42.2493037956085</v>
+        <v>42.24930376964512</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>13.67665957840235</v>
+        <v>13.67665960908966</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.5610043969379358</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.0094212539627038</v>
+        <v>-0.0094212539386657</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>315.5624010368569</v>
+        <v>315.5624010368568</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>123</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>44.8115875236479</v>
+        <v>44.81158764587864</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>18.80330487713629</v>
+        <v>18.80330495046831</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.9594169744013864</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.2936791870994364</v>
+        <v>-0.2936791884213454</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>314.1988565073529</v>
+        <v>314.1988565073528</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>39.4</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>25.51890100136104</v>
+        <v>25.51890098340624</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>22.15949855776235</v>
+        <v>22.15949860261393</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>1.466304227874723</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.0510560166855862</v>
+        <v>-0.0510560167216406</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45.6130985545125</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>17.14796132572135</v>
+        <v>17.1479613745858</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.6339136546416103</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0200702556135994</v>
+        <v>0.0200702555724076</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>40.56791781121216</v>
+        <v>40.56791792989179</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>8.795121504622108</v>
+        <v>8.795121473559771</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>3.424403678043964</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.012219334662393</v>
+        <v>-0.0122193349508064</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>51.19826193452269</v>
+        <v>51.19826187258602</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>15.2186302517052</v>
+        <v>15.21863021220717</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.9030113209428468</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.0285624980738061</v>
+        <v>0.0285624980497713</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>44.69855608764271</v>
+        <v>44.69855590727504</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>11.91849483873356</v>
+        <v>11.91849501421324</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.6923452660340564</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.0142997063541132</v>
+        <v>0.0142997064382348</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>40.96780409595357</v>
+        <v>40.96780407414035</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>15.0078626626141</v>
+        <v>15.00786257139901</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.8533029515682156</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.2968933835575527</v>
+        <v>-0.296893383797902</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>47.19311138842279</v>
+        <v>47.19311120937765</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>11.39362600998784</v>
+        <v>11.39362595162503</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.8195863752730295</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.1184162340291065</v>
+        <v>-0.1184162339209535</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>300.464414257338</v>
+        <v>300.4644142573372</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>15.05</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>45.3342759832075</v>
+        <v>45.3342748045228</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>15.67851675041665</v>
+        <v>15.67851693903423</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.5960283827930377</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.0399223497683689</v>
+        <v>0.039922350080819</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>37.98031141471911</v>
+        <v>37.98031142306747</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>13.96963024085091</v>
+        <v>13.96963020129108</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.6908969068824943</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.1346190727337225</v>
+        <v>-0.1346190727938145</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>40.66036588080277</v>
+        <v>40.66036588733662</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>8.223988289616511</v>
+        <v>8.223988209225968</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>1.346732389413241</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-1.50437670401157</v>
+        <v>-1.504376704372067</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>42.74444914265271</v>
+        <v>42.74444918787216</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>18.17966150893134</v>
+        <v>18.17966170621498</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.7162055506791973</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>1.70530452121731</v>
+        <v>1.705304520496283</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>285.2889614112211</v>
+        <v>285.2889614112212</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>41.7</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>35.64211764050505</v>
+        <v>35.64211761188942</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>30.29998881049124</v>
+        <v>30.2999887353088</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.7965600108822152</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.0540074943756485</v>
+        <v>0.0540074941593327</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>38.42614821649553</v>
+        <v>38.42614801351538</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>19.84659258831453</v>
+        <v>19.84659272412114</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>1.197008588366594</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.0220949050265305</v>
+        <v>0.022094905086616</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>20.53694523868049</v>
+        <v>20.53694549550553</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>52.02045842495172</v>
+        <v>52.02045850696904</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.9525940395007158</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>39.74984822361273</v>
+        <v>39.74984793674872</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>7.70376991014376</v>
+        <v>7.703769945583962</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.8712159302658704</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.3529885477025689</v>
+        <v>0.3529885485437671</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>40.25596313736538</v>
+        <v>40.25596307762549</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>38.58841472978836</v>
+        <v>38.58841476229827</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.5152476493270745</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.1533933914070475</v>
+        <v>0.1533933914791558</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>245.3828784140551</v>
+        <v>245.3828784140557</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>18.7</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>49.87871702605914</v>
+        <v>49.87871714265764</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>18.18088842248087</v>
+        <v>18.18088851388626</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.504443825246352</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.0671892186569481</v>
+        <v>0.0671892186809854</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>244.7355820913302</v>
+        <v>244.7355820913301</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>19.1</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>53.94208575956069</v>
+        <v>53.94208568557162</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>17.37582535371113</v>
+        <v>17.37582538737434</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.8659938254061945</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.0434868266882373</v>
+        <v>0.0434868267363081</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>43.13680147100673</v>
+        <v>43.13680153712667</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>14.42920128653862</v>
+        <v>14.42920119053669</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.553497880980222</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.0245257739918884</v>
+        <v>-0.0245257740880242</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>48.47682869611716</v>
+        <v>48.47682866085793</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>8.067261193509751</v>
+        <v>8.067261224694033</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.7397833596138054</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.0135409435084282</v>
+        <v>0.0135409435444792</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>40.96869960835159</v>
+        <v>40.96869967058876</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>8.560072786603298</v>
+        <v>8.560072778015133</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.7489058977158836</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.1637533328637236</v>
+        <v>-0.1637533327916138</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>238.8212411154094</v>
+        <v>238.8212411154095</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>9.74</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>52.04701545584121</v>
+        <v>52.04701536515427</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>9.477770553644785</v>
+        <v>9.47777054404639</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.0900261751395376</v>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>237.5489720767549</v>
+        <v>237.5489720767534</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>27.5</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>38.37936137881584</v>
+        <v>38.37936119973475</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>10.94307858729346</v>
+        <v>10.94307861932476</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>1.140767597832503</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.0109170887932509</v>
+        <v>0.0109170888052669</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>31.75901720089503</v>
+        <v>31.75901715377957</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>34.60831379317314</v>
+        <v>34.60831377907355</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.3028533853000185</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.0079219895256344</v>
+        <v>-0.0079219894655497</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>41.42784983512857</v>
+        <v>41.42784931073984</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>6.385750490031016</v>
+        <v>6.385750482770764</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.7117997536021536</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.001048098020485</v>
+        <v>-0.0010480977921564</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>222.6409706967641</v>
+        <v>222.6409706967646</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>66.2</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>44.01882586406715</v>
+        <v>44.01882572850487</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>6.962992613169232</v>
+        <v>6.962992544494272</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.5733912935333961</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.0474101719949142</v>
+        <v>0.0474101725957821</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>221.7567918734796</v>
+        <v>221.7567918734798</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>16.95</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>51.2999157214879</v>
+        <v>51.29991557299225</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>9.531192990130831</v>
+        <v>9.531192862571078</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.477141843300783</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.0383254296978489</v>
+        <v>0.0383254297699514</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>220.6955093163317</v>
+        <v>220.6955093163316</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>7.15</v>
@@ -11155,7 +11155,7 @@
         <v>33.7836140598308</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>22.88948662210482</v>
+        <v>22.88948700813747</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>1.017875094654934</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.0098385618904851</v>
+        <v>0.0098385620779544</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>50.32130323475831</v>
+        <v>50.32130305785812</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>17.80345371397125</v>
+        <v>17.80345379711126</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.5740484881769992</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.0426544736790749</v>
+        <v>0.0426544737752131</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>36.84470713346157</v>
+        <v>36.84470761564385</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>18.50978412859796</v>
+        <v>18.50978417548545</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.3735846693174758</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.0523507363751032</v>
+        <v>-0.0523507362549235</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>45.89110498188362</v>
+        <v>45.89110500723822</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>9.079728223280265</v>
+        <v>9.079728462273602</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.7599372653581888</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0208318080526453</v>
+        <v>-0.020831808244919</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>210.1352860212555</v>
+        <v>210.1352860212554</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>51.6</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>39.63429149046649</v>
+        <v>39.63429151452108</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>15.97904096054062</v>
+        <v>15.97904100958472</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.7470294224524175</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.0842606244140337</v>
+        <v>-0.08426062431789361</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>206.946996316704</v>
+        <v>206.9469963167012</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>74</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>43.9677791843522</v>
+        <v>43.96777869308752</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>15.21026727620951</v>
+        <v>15.21026750003443</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.331525328606285</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0255426099646984</v>
+        <v>-0.0255426087629699</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>41.06843205045118</v>
+        <v>41.06843207331551</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>51.84888247847834</v>
+        <v>51.84888246109941</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.1739214130846817</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0346456114602347</v>
+        <v>0.0346456114842701</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>36.7294611433726</v>
+        <v>36.72946108274844</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>13.05098986402571</v>
+        <v>13.05098986731406</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>1.056147262275732</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.560594389918736</v>
+        <v>-0.5605943895582151</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>40.88989438490316</v>
+        <v>40.88989407943616</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>11.94939780867888</v>
+        <v>11.94939788530996</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.6567916430582257</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.2193762473805298</v>
+        <v>0.2193762468998428</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>39.78504774009384</v>
+        <v>39.78504674408627</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>5.876276768703613</v>
+        <v>5.876277000455783</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>1.47494973357797</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.0540444811194017</v>
+        <v>0.0540444822730614</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>32.83723744923304</v>
+        <v>32.83723734070885</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>39.29058378582489</v>
+        <v>39.29058376628727</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.3731044926307865</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>198.3324418996713</v>
+        <v>198.3324418996709</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>6.91</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>47.80918218981311</v>
+        <v>47.80918228683141</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>8.903268537060773</v>
+        <v>8.903268966712973</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.4517457215208968</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.0117361760403098</v>
+        <v>0.0117361762181668</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>40.97468008103634</v>
+        <v>40.97468019130149</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>9.069341420771137</v>
+        <v>9.069341584262196</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.6141731338747058</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.0200691473525492</v>
+        <v>-0.0200691474006242</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>176.0798424999867</v>
+        <v>176.0798424999866</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>85.40000000000001</v>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>37.81701907264216</v>
+        <v>37.81701884049562</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>25.41798016647997</v>
+        <v>25.41798050316604</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.4582600718857885</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.0923674493857085</v>
+        <v>-0.0923674492655308</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>42.86200956555047</v>
+        <v>42.86200919382448</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>13.84994508851397</v>
+        <v>13.84994488719358</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.9331807990953142</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.0180296572893009</v>
+        <v>-0.0180296572652666</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>49.80275979459553</v>
+        <v>49.80275954194952</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>12.91781131450254</v>
+        <v>12.9178114708333</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.4841207299581113</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.0380862427424459</v>
+        <v>0.0380862428265657</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>40.87213865981703</v>
+        <v>40.87213848357283</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>17.95372637921292</v>
+        <v>17.95372640362756</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.491292501042884</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.068148647843513</v>
+        <v>-0.0681486477714091</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>27.63814910385121</v>
+        <v>27.63814919797564</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>19.11026769157297</v>
+        <v>19.11026774814908</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>2.080997550165212</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.09834711706084399</v>
+        <v>-0.09834711710891431</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>162.2099687293949</v>
+        <v>162.209968729395</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>18.8</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>45.00525870856238</v>
+        <v>45.00525864606608</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>9.404393840146151</v>
+        <v>9.404393840146149</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.7232765328707211</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.0132923188847451</v>
+        <v>0.0132923188366741</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>45.90764572700009</v>
+        <v>45.90764556512796</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>15.05820109353988</v>
+        <v>15.05820107813317</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>1.005758675899875</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0444535163112265</v>
+        <v>-0.044453516167022</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>149.8697964466309</v>
+        <v>149.869796446631</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>41.35</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>49.23285930779615</v>
+        <v>49.23285912710725</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.58832534793349</v>
+        <v>18.58832522358178</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.6781049132765414</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.0092848753974494</v>
+        <v>-0.0092848753373655</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>131.4920285481475</v>
+        <v>131.4920285481522</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>12.8</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>41.77639390313529</v>
+        <v>41.77639378666424</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>17.52518046305482</v>
+        <v>17.52518051967246</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.5891277805561076</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.0155391404378197</v>
+        <v>-0.0155391404137841</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>48.80848324117815</v>
+        <v>48.80848322919812</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>9.016712847570927</v>
+        <v>9.016712869464961</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.1254619574400108</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.1272969761102128</v>
+        <v>0.1272969760861699</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>33.25920837915064</v>
+        <v>33.25920822879918</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>15.44093213213244</v>
+        <v>15.44093229509874</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>1.002633787291489</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0189842606614609</v>
+        <v>0.0189842609739052</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44.22282616026612</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>16.95566938817193</v>
+        <v>16.95566928583239</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.27538356894205</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.0140126297989625</v>
+        <v>0.0140126297869447</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v/>
       </c>
       <c r="D227" s="2" t="n">
-        <v>69.66104626006957</v>
+        <v>69.66104626006032</v>
       </c>
       <c r="E227" s="2" t="n">
         <v>7.92</v>
@@ -12477,10 +12477,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>44.489513394395</v>
+        <v>44.48951306429618</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>14.13477407630072</v>
+        <v>14.13477429389725</v>
       </c>
       <c r="J227" s="2" t="n">
         <v>1.291622770834358</v>
@@ -12495,7 +12495,7 @@
         <v>-1</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>-0.0047407273838121</v>
+        <v>-0.0047407273597766</v>
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
